--- a/src/attributions/attributions_ig_traj_174.xlsx
+++ b/src/attributions/attributions_ig_traj_174.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,160 +999,160 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.107670151431414</v>
+        <v>0.08539595389750285</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2053876115891933</v>
+        <v>0.1214509199635201</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.000870470479885202</v>
+        <v>-0.06347933047612019</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01825145604069086</v>
+        <v>0.01888005578631054</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2064948814758124</v>
+        <v>0.04949500572033638</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00208025141448778</v>
+        <v>-0.01590638296965586</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09778338212392844</v>
+        <v>0.03403680381173914</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01432430740601758</v>
+        <v>-0.1225578899588171</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04174952113749071</v>
+        <v>0.02456171730798556</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.07844340024108128</v>
+        <v>-0.05474031532578731</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01123724989979894</v>
+        <v>0.01591441968873292</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.00467995902030148</v>
+        <v>-0.02059785104242284</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03477317437924476</v>
+        <v>0.10769558072862</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02975591359928845</v>
+        <v>-0.02596656058043971</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06894031625633901</v>
+        <v>0.1991879374883998</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1504158949591624</v>
+        <v>0.2376621427303892</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.06762809990804736</v>
+        <v>-0.01136563078868094</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01316411438484101</v>
+        <v>0.05229061998571615</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1161,79 +1161,79 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.03736677967854636</v>
+        <v>-0.07759712834295697</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.07026386262018187</v>
+        <v>0.07518376219352413</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.02677008819260617</v>
+        <v>-0.09526598561044637</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01906614199068762</v>
+        <v>-0.06484745566175511</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.05327664047297926</v>
+        <v>-0.1059284101847116</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.06915173979540963</v>
+        <v>-0.04548770502300087</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.01804737642947697</v>
+        <v>0.06463066149122079</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01512898727912453</v>
+        <v>-0.1293825091202307</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.005352203034577101</v>
+        <v>-0.008459591018283124</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,55 +1242,55 @@
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0336355770062513</v>
+        <v>-0.1108520658806269</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03569317361011079</v>
+        <v>-0.05027645989854917</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0251507005628732</v>
+        <v>-0.01628225745160151</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01586600892987506</v>
+        <v>-0.09335044417464583</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02594067695371425</v>
+        <v>0.09539743740925401</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05198710927025178</v>
+        <v>-0.001496821198243206</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
@@ -1299,52 +1299,52 @@
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04516854268119422</v>
+        <v>-0.1109409874364566</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.03815737946181457</v>
+        <v>-0.04126966560818436</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01954564062428951</v>
+        <v>0.01054530945080332</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04358123142453846</v>
+        <v>-0.07734324679628708</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01717012150273894</v>
+        <v>0.03343519141106763</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04988333764285281</v>
+        <v>-0.01697955053350071</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02121619411584265</v>
+        <v>-0.008424213159395134</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.03359901195050785</v>
+        <v>-0.002844614657192428</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01385797544263802</v>
+        <v>0.05942516679944551</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,49 +1377,49 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05212903656296591</v>
+        <v>0.02140569107752717</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.004971154324998677</v>
+        <v>0.08358890339507188</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02718932500684638</v>
+        <v>0.2212704723251272</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.05015491900709527</v>
+        <v>-0.08763851148805207</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.07613886383889099</v>
+        <v>0.2042793179845724</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.0199689068547195</v>
+        <v>0.0258950774491685</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04747992163333337</v>
+        <v>-0.07306583713874158</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03421357883596667</v>
+        <v>0.03289894938905859</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.04056784176355664</v>
+        <v>0.01161505907008398</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1458,25 +1458,25 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.047632734695192</v>
+        <v>-0.1343905735405545</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03127982317017986</v>
+        <v>-0.02428406583464976</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02441504420193668</v>
+        <v>-0.005028201682153059</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
@@ -1485,25 +1485,25 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.0002063141115742818</v>
+        <v>-0.1292907173202251</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.01377775761390556</v>
+        <v>-0.01752211420037452</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.001886070509032845</v>
+        <v>0.06511516297342031</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>0</v>
@@ -1512,43 +1512,43 @@
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01316388935840617</v>
+        <v>-0.09187149678477263</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.0009316850821103231</v>
+        <v>0.2124512419297892</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0192548302470746</v>
+        <v>-0.06847036651840219</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03444598377532641</v>
+        <v>-0.04936798894289306</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.04121121055052257</v>
+        <v>0.003772538662248939</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,169 +1568,169 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.03794235115037941</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01352425431882531</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.03955088528172958</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.01561273936373942</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.002788890888181847</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.008479631866996308</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.01986064953311059</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.04054054590646931</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.0191382587234786</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.01110569413712595</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.02800769386726264</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.027269781896966</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.0100459353877585</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.04299462647814389</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.00593373326674969</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.0371366608267981</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.05405480999724933</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.03615158499804883</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.006015047711124722</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1742,40 +1742,40 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.03320484766675465</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.008225830173190261</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.02710442223434018</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.05595003497401592</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.002614780545073841</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,61 +1784,61 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.004684649428003159</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.01392690158354713</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.006623837058917125</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.0286039279450255</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02789646482034315</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.01814311794302952</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.003847744808952275</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.06476222353622953</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.020801152004382</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.02546958486444477</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03478184721447129</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.02625270856214951</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0.002165418113195802</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.0437329712793187</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.004373198171625767</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01556953660399107</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.02815631325080557</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0.0006231648105706646</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,37 +1946,37 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.0009472076230728457</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.03442934468405462</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.05843813793905264</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.02396922881251595</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.01325068684824028</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.01206835893107172</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.01817665017261243</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.05497135282863247</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.008850892581242324</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.03426084674915226</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,99 +2039,7496 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.04463585556568356</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.02958233871179826</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.02589941659222729</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.02656102367618569</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.006254308011034436</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.0186695672765483</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.04933539050210311</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.02401561942591808</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.009496592533004224</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.03254866530105339</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4036313167286551</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1494316403570793</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3611163889943622</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2121136640351358</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.001897726482349403</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0680078896172442</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1825437891813148</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1204393823088725</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1044198737536152</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.155199605261009</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1403782815347278</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1985194735742055</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.09091240716682643</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.06577693983857937</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2354337590466969</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.4393761931878268</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.3196487168146946</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.4830790327883757</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.2384437903664677</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.1964598591590286</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.2010569873731169</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.05007302024079525</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1039558625370042</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.16882382920411</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.06546384929352567</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.04524213081828476</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.1238481509724415</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2605994105837615</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.07796036340197164</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1980424447698439</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.3094576288144175</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.02699430070680692</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.2493039807257467</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2498366477395129</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.07273080742048524</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1680965555372344</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.09928667700521401</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.05005392376325794</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1883060003080421</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.1516605494733728</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.009537975091269177</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.02578611177854097</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1940674252872833</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.1288586882340899</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1818255382544851</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.08925169615713056</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.1184114414545799</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1539617336053402</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1468179660745631</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.2392440251656017</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2401980874073375</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2280774168526322</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1311567485871897</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1759391426661392</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.06690885092769915</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.1148880723924748</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.3333062647156513</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.05791569120725987</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>-0.03819264876842041</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-6.910958346158461e-05</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.08612262126056619</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1296769871588071</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3718259492461672</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03578355767655557</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2141026008249552</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.199353329468837</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.03754730184135106</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1748821873728437</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1078161140636102</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1254402740337456</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.06163391317416488</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.01350681237857025</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2576729602483571</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.03073067907084731</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1508051683148338</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1115124800685355</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.09371901243833204</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.5060145815733341</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1647339569216624</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1604919510302465</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.0401813071502683</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.05135595060913389</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1333172818581236</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.02333711177323575</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.07083606038784791</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1045610207734292</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.1231876376780124</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.006415909485503551</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.1454875668119325</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.1885521231752209</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.04537174344198711</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1725975610398982</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1580870453844656</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.1258992989924521</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.00663136995291753</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1727219339764586</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.01643571026242561</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1869320940439932</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.04157354368648039</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1310168513805193</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0416299010912086</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.09662559048062452</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.01735799566406896</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0389752546448878</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.01307524124787518</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.09191374228882414</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.2007830345560108</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.05732611481579571</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.08743649128978627</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.08031448187255923</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1217963834018158</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.09990514144189887</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.05985117658650701</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.188283832453892</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.05566242082051933</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1673938648371769</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.208627199151461</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.06511330910687237</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.2230423828582969</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.019332753020903</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.004976826398385755</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1604233460688551</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.07857384322073449</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1219487321216715</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.401675561002995</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05419900888505837</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2413584851087376</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2725395176319334</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.02571311110305717</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.174476441565915</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.10112707529493</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.141620300054794</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.03520753959860037</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.06134118824724257</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2550529482108098</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1165758524093639</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1557715581149522</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1074224172472965</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.0945193741348684</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.5297649136250011</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1338930712925531</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.1975258096496916</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.05747903063289539</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.0855066623984377</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.2253661584339463</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.008250180245763617</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.08549153209055081</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.04969234331860071</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.123143575011744</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.0002724973339551881</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.06571477389941779</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2053010765110247</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.05400057241072555</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1516853545831983</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.2365755889057866</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1205651690554122</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.06593829809011544</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.1899655820100236</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.05010530919202751</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1488637970086909</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.05732499783733309</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.05817200447664678</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.01454716118963555</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.08442486818696865</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.03917132640522938</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1291395260274131</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.0316451487853989</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1480624132724968</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.1236730133104632</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.07240810673265714</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.06058106099012885</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.0551196193156947</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.09152307986925166</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.07219372256929744</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1432143840286988</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2098441510041789</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.07633770919351662</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1285890991611138</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.2448671818165644</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.07816151483272146</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2359360824202309</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.03380734206769661</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>-0.01011465550138437</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1352111347802392</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.05442429791891034</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.05071433901047761</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6432143132278254</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.05216528209493398</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1666541931755777</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1753772066445888</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5441427895754588</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1655708834269826</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0259943525732654</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.0971742066615829</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05034759460402229</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.09277174158774716</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.08299636333940022</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01379890713163495</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.07390260463791351</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3687747919113651</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.1905941117072193</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.1229710341456541</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2433692123392741</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1436206236238155</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1891758203569519</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1996702587137277</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.4210577054296206</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.01075047586891287</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.02491888161328604</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.09117705120914153</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.218654779417324</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.1161572578726723</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.1029194677458144</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.2403063064098255</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.04941883341673375</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.0505857883007399</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1795332746889092</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.03382211502118573</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.1168278550215091</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.005619238301696996</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0452106783503996</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.06396584035584982</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.2501539473929364</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07901526893827591</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.1033245596795277</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.09903087486071231</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.2004210677415795</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1426896884701472</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0.05505645921310988</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.2132472366756371</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.2293218228342218</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.05159003421161461</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.09676360405138126</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.08359386350254909</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.03698478345436169</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-0.05187450233144077</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.5415600754603515</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.01515789901393343</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.15626835404261</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>-0.03710618320977364</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.04949866818550003</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.1737644344298825</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.07129968365296138</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.07087741387032835</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.1088418179664531</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.003903013270506704</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.1042385281526906</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.1088646817950288</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.05697087530686894</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>-0.03052881377362612</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.0989827775419528</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.09571285429078227</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.07997745273301923</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.244339090426516</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.2533291684967253</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.05575673812911786</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.1471528702081958</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.05967741424986193</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.2100768747920235</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.09984238704968573</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.06902031831146727</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.3228956603265572</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1860090732379993</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.2500123096181698</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.02209300414996733</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.03326246423441589</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.113370305632612</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.2031183601026385</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.08976124287160686</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2693989692191348</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0101052070652434</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1747128798856366</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1755158410945009</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09122378250854878</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.09855351691101745</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.09248362300625072</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.0006827768688695925</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.06322408516717691</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.04852663807827413</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.09037995537078689</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.01773432566707462</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.09528779725264214</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.1043971348953696</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.09605975449610916</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2678199819042757</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.01425313354744216</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.06027273385488901</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08230259501526779</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2244801332565573</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.12401984460595</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.04376273499531366</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.04412185521255464</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.02317188165753576</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.1152777166786605</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.01353352501184888</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.02501069884207137</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.124011470909348</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.007213065776158975</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.05799630462074823</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1274538466066894</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1376033707373006</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.0287324042597421</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1158513435869523</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.006817625278669079</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.05449828347577998</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.001881052273626027</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.09267009653179265</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.03482981674172889</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.05902862146484431</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.007108597437165526</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.004157741034165677</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.0006862343604039732</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.01748186549200775</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>-0.01748543684090996</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.07527306849661039</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.003186137194554029</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.003773907927846821</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.07831928011245881</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.09194409132481707</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.136112975993796</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1371957615883365</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.0128526966284343</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.04992371285472547</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1244643083220685</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.05876045938328242</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.03568836245337535</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.09901728994372348</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.01618538293163933</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.0122051208519231</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.1187716709401326</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.02892397937456909</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4360937586669202</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03338935504654489</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2208946976096831</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5077509026985516</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.05289338838334411</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1511729711546471</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.08828123022258004</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.03838678586057832</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0825844050426387</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.003224796484125896</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.04275643465690707</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.05303786940589074</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1291658052089158</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.05836119269074723</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.08257866361106134</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.4491133943501669</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.1765866365318904</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.1666254806174195</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.09186689672224753</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.01413417348207277</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.04702077481227696</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.05567192361698289</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.08424707865231816</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.04898436322884042</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1672637685713026</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.01390756798625237</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.04691326756972411</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1730320409574365</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.007893355549160855</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.06645559386618051</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.06791285912458851</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.07200919016141952</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.02303070411647224</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1633090683941729</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.0006817779036523111</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.07715192846505506</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.01016071949050904</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.0210705683972914</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.08677150076862744</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.0727657269875689</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.05325634331835007</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.0869347700989852</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.09033123036433559</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.031686696731201</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.07608635738068381</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.1131859073833441</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.02900142515344775</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.02499549534643221</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.1055743363597936</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.009514824985187922</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.05859636731772035</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.1814619318203103</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.02768514352672874</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.08113907935692416</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.0539324027195158</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.01864716164217084</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.08081193696642036</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.1381514249078422</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.08298339714018366</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.005880427738694257</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1179028604297023</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.05816238903477327</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.201782885805717</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7796898021764335</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1808905874698749</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.356967574355395</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.087208585505608</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01712874093551497</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.08492734862993299</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.07921184242924162</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.0722160102265484</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.2640094164557729</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.3575173842733917</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3345247345609167</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.3338042813969546</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.3195374014695522</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.3440961213385595</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.9066930776557394</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.4406186689732265</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.2514913037773314</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.02636122655655442</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.0009255281795978306</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1543409696301041</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0.1282033982530767</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.006981697986935036</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.008224166505969402</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.305545692352598</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.4133884922950756</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.04838011243799989</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.4495104580224301</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.3442889297911473</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.1008986271666737</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.1926065901603073</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.3982906812156931</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1221179373218663</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.4317143706321406</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.3493833573888591</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.02355446361115385</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.232815754731957</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.1218344257860914</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.01098746151918809</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.194962704600697</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.1835452327378587</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.1436765264525418</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.1048837000882928</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0.05099372519475236</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.1638954999650184</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.4069267246852744</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.291069764877843</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.009173909201101695</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.2721646732007155</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.2307884732450358</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.07041218291078043</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.5107273888903184</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.3897330849916732</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.1006231912984967</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.2111949464708364</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0.298047083854858</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.2620243617291151</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.4166098861665652</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0.01906645212317576</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.0872204919167322</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.2429894961873629</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.1330625489392082</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8201982303265568</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2856028852484281</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.7517421016009412</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.027750979643394</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.8896327481670662</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.875566126461332</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.2479646099607913</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.181020687120302</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1193934150137416</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.211525061415752</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.3900590054079175</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1809360355722753</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.316670480692462</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1087086466012727</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.1514384289502892</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.601652994434226</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2447517938968448</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.5386363971908255</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.5550311856360464</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.2414507124034931</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.001440162408664457</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.1333962426938703</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.1693328073649228</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.1232964432530582</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.6116697923534484</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.2170438029351986</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.3002565138420575</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.3020768159126142</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.170806940936108</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.1934053789602982</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.2906196403500929</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.353709968711982</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1575869518920472</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.267670024023798</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.1657468316536151</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.2593091775107959</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.2142250703197739</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.3625333355198901</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.2494367823643885</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.100138706777822</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.08741701757664759</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.16399272716267</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.2985976867327947</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.08122305257699178</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.0409759535499578</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.1922961089290733</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.1328098924379702</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.08816248299036697</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.1667310992627386</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.0107374262169542</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1780235912052323</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.3353759627324941</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.1075312553504576</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.2271406555925104</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0.1935332986380662</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.09164464417187074</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.2278183601319178</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.1456725517972066</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.36111669863137</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.1543233162179783</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0006198923121755739</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.05527164371485965</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9245743828721072</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.4691675726971176</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1672805927862393</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9037560745531809</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.6442079991879728</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.1125758938652257</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1989222270551714</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.1287241873261885</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.004600714595648636</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.02803065271143313</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.3272729433967189</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.002931812770704408</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.2602963135576046</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.08796767914394109</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.2709596545208369</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.7435873294119582</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.1815033926416931</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.3136121042448002</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.06513801403821103</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.1896545316795506</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.06256356645669921</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.0219633886687833</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.004824904617835667</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.02392570074798646</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.5105194308606337</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.179942370400605</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.1112370494378095</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.3134701133168247</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.1628939642285576</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0.0580958038735057</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.2198912561875215</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.308595786675614</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.2209079436430479</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.3102474117819374</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.187613114466148</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>-0.02391059017016119</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.2389628805927723</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.1051404327839711</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.1384408494795075</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.2007242168964089</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>-0.05121941068022871</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.004985026920643013</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.1712947365775396</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.01319602450644088</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.06231168274974779</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.2361919846803786</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.1615348062598025</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0.05573502586889351</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.1551103020235739</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.117367508260504</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.06199327290302595</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.3535853853140313</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.2099121938088286</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.05484633388350661</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0.1086776908867476</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.1748484368484225</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.1672962145511032</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.3678602691489051</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.1073477000483014</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.1974715160260129</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.1936421269612184</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.1153089829790948</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
